--- a/outputs/aco_schedule_formatted.xlsx
+++ b/outputs/aco_schedule_formatted.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6178" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6180" uniqueCount="690">
   <si>
     <t>offering_id</t>
   </si>
@@ -2046,31 +2046,25 @@
     <t>Schedule Source</t>
   </si>
   <si>
-    <t>Constraint-first repair after incomplete metaheuristic result</t>
-  </si>
-  <si>
-    <t>Metaheuristic Time (seconds)</t>
-  </si>
-  <si>
-    <t>21.65</t>
-  </si>
-  <si>
-    <t>Constraint Repair Time (seconds)</t>
-  </si>
-  <si>
-    <t>145.29</t>
+    <t>ACO Metaheuristic Search + Integrated Decoder</t>
+  </si>
+  <si>
+    <t>ACO Search Time (seconds)</t>
+  </si>
+  <si>
+    <t>7.67</t>
+  </si>
+  <si>
+    <t>ACO Best Fitness Score</t>
+  </si>
+  <si>
+    <t>-591939761</t>
   </si>
   <si>
     <t>Total Computation Time (seconds)</t>
   </si>
   <si>
-    <t>166.94</t>
-  </si>
-  <si>
-    <t>Final ACO Fitness / Energy Score</t>
-  </si>
-  <si>
-    <t>-700943892</t>
+    <t>134.84</t>
   </si>
   <si>
     <t>Total Scheduled Meetings</t>
@@ -2079,13 +2073,22 @@
     <t>1010</t>
   </si>
   <si>
-    <t>Total Unscheduled Meetings</t>
+    <t>Unscheduled Meetings</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
     <t>Hard Constraint Violations</t>
+  </si>
+  <si>
+    <t>Total Constraint Violations</t>
+  </si>
+  <si>
+    <t>Schedule Status</t>
+  </si>
+  <si>
+    <t>PASS — 0 hard violations</t>
   </si>
 </sst>
 </file>
@@ -47405,7 +47408,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
@@ -47469,15 +47472,23 @@
         <v>686</v>
       </c>
       <c r="B8" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>687</v>
+      </c>
+      <c r="B9" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>688</v>
       </c>
-      <c r="B9" t="s">
-        <v>687</v>
+      <c r="B10" t="s">
+        <v>689</v>
       </c>
     </row>
   </sheetData>
